--- a/rawdata/readcounts/CleanVersion.xlsx
+++ b/rawdata/readcounts/CleanVersion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gwm297/GitHubRepos/SeaChange.WP5.2/rawdata/readcounts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{90782272-E522-FE44-88E8-1718F253E751}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8189393-0CAA-924C-ABF0-BF89F3E8965E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31380" yWindow="600" windowWidth="29600" windowHeight="20840" xr2:uid="{E2B846F4-E4CC-EB4D-B889-CA33870CE4FF}"/>
+    <workbookView xWindow="9260" yWindow="600" windowWidth="29600" windowHeight="20840" xr2:uid="{E2B846F4-E4CC-EB4D-B889-CA33870CE4FF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -95,15 +95,6 @@
     <t>120964.3 ± 242237</t>
   </si>
   <si>
-    <t>163145.1 ± 186709.2</t>
-  </si>
-  <si>
-    <t>28.2 ± 54.2</t>
-  </si>
-  <si>
-    <t>77307.2 ± 116481.7</t>
-  </si>
-  <si>
     <t>32951.2 ± 60635.9</t>
   </si>
   <si>
@@ -132,6 +123,15 @@
   </si>
   <si>
     <t>49114.5 ± 80723.3</t>
+  </si>
+  <si>
+    <t>217275.1 ± 190959.5</t>
+  </si>
+  <si>
+    <t>30.6 ± 55.8</t>
+  </si>
+  <si>
+    <t>133766.2 ± 128025.6</t>
   </si>
 </sst>
 </file>
@@ -589,10 +589,10 @@
         <v>9</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F5" s="2"/>
     </row>
@@ -605,10 +605,10 @@
         <v>10</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F6" s="2"/>
     </row>
@@ -621,10 +621,10 @@
         <v>11</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F7" s="2"/>
     </row>
@@ -642,7 +642,7 @@
         <v>21</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F8" s="2"/>
     </row>
@@ -658,7 +658,7 @@
         <v>22</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F9" s="2"/>
     </row>
@@ -674,7 +674,7 @@
         <v>23</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F10" s="2"/>
     </row>
@@ -689,10 +689,10 @@
         <v>15</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F11" s="2"/>
     </row>
@@ -705,10 +705,10 @@
         <v>16</v>
       </c>
       <c r="D12" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="6" t="s">
         <v>25</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>28</v>
       </c>
       <c r="F12" s="2"/>
     </row>
@@ -721,10 +721,10 @@
         <v>17</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F13" s="2"/>
     </row>
@@ -738,5 +738,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>